--- a/social_worker_forms/032_social_support_assistance_request_form--social_worker_forms.xlsx
+++ b/social_worker_forms/032_social_support_assistance_request_form--social_worker_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Contact Name</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>phone_number_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone Number 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Submitter Department</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Submitter Name</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Submitter Email</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Submitter Phone</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Review Status</t>
+          <t>Review Status2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Submitter Department2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Submitter Name2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Submitter Email2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Submit Date</t>
+          <t>Submit Date2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1501,7 +1501,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1518,7 +1518,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
